--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_28-11-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_28-11-2025.xlsx
@@ -588,30 +588,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c35aa235
-	0x7ff7c3302630
-	0x7ff7c30916dd
-	0x7ff7c30ea27e
-	0x7ff7c30ea58c
-	0x7ff7c313ed77
-	0x7ff7c313baba
-	0x7ff7c30db0ed
-	0x7ff7c30dbf63
-	0x7ff7c35d5d60
-	0x7ff7c35cfe8a
-	0x7ff7c35f1005
-	0x7ff7c331d71e
-	0x7ff7c3324e1f
-	0x7ff7c330b7c4
-	0x7ff7c330b97f
-	0x7ff7c32f18e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£15.52</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -708,30 +685,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c35aa235
-	0x7ff7c3302630
-	0x7ff7c30916dd
-	0x7ff7c30ea27e
-	0x7ff7c30ea58c
-	0x7ff7c313ed77
-	0x7ff7c313baba
-	0x7ff7c30db0ed
-	0x7ff7c30dbf63
-	0x7ff7c35d5d60
-	0x7ff7c35cfe8a
-	0x7ff7c35f1005
-	0x7ff7c331d71e
-	0x7ff7c3324e1f
-	0x7ff7c330b7c4
-	0x7ff7c330b97f
-	0x7ff7c32f18e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£18.20</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -828,30 +782,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c35aa235
-	0x7ff7c3302630
-	0x7ff7c30916dd
-	0x7ff7c30ea27e
-	0x7ff7c30ea58c
-	0x7ff7c313ed77
-	0x7ff7c313baba
-	0x7ff7c30db0ed
-	0x7ff7c30dbf63
-	0x7ff7c35d5d60
-	0x7ff7c35cfe8a
-	0x7ff7c35f1005
-	0x7ff7c331d71e
-	0x7ff7c3324e1f
-	0x7ff7c330b7c4
-	0x7ff7c330b97f
-	0x7ff7c32f18e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£21.50</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -948,30 +879,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c35aa235
-	0x7ff7c3302630
-	0x7ff7c30916dd
-	0x7ff7c30ea27e
-	0x7ff7c30ea58c
-	0x7ff7c313ed77
-	0x7ff7c313baba
-	0x7ff7c30db0ed
-	0x7ff7c30dbf63
-	0x7ff7c35d5d60
-	0x7ff7c35cfe8a
-	0x7ff7c35f1005
-	0x7ff7c331d71e
-	0x7ff7c3324e1f
-	0x7ff7c330b7c4
-	0x7ff7c330b97f
-	0x7ff7c32f18e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£22.89</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1068,30 +976,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c35aa235
-	0x7ff7c3302630
-	0x7ff7c30916dd
-	0x7ff7c30ea27e
-	0x7ff7c30ea58c
-	0x7ff7c313ed77
-	0x7ff7c313baba
-	0x7ff7c30db0ed
-	0x7ff7c30dbf63
-	0x7ff7c35d5d60
-	0x7ff7c35cfe8a
-	0x7ff7c35f1005
-	0x7ff7c331d71e
-	0x7ff7c3324e1f
-	0x7ff7c330b7c4
-	0x7ff7c330b97f
-	0x7ff7c32f18e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£26.90</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1188,30 +1073,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c35aa235
-	0x7ff7c3302630
-	0x7ff7c30916dd
-	0x7ff7c30ea27e
-	0x7ff7c30ea58c
-	0x7ff7c313ed77
-	0x7ff7c313baba
-	0x7ff7c30db0ed
-	0x7ff7c30dbf63
-	0x7ff7c35d5d60
-	0x7ff7c35cfe8a
-	0x7ff7c35f1005
-	0x7ff7c331d71e
-	0x7ff7c3324e1f
-	0x7ff7c330b7c4
-	0x7ff7c330b97f
-	0x7ff7c32f18e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£33.11</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1308,30 +1170,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c35aa235
-	0x7ff7c3302630
-	0x7ff7c30916dd
-	0x7ff7c30ea27e
-	0x7ff7c30ea58c
-	0x7ff7c313ed77
-	0x7ff7c313baba
-	0x7ff7c30db0ed
-	0x7ff7c30dbf63
-	0x7ff7c35d5d60
-	0x7ff7c35cfe8a
-	0x7ff7c35f1005
-	0x7ff7c331d71e
-	0x7ff7c3324e1f
-	0x7ff7c330b7c4
-	0x7ff7c330b97f
-	0x7ff7c32f18e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£34.47</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1428,30 +1267,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c35aa235
-	0x7ff7c3302630
-	0x7ff7c30916dd
-	0x7ff7c30ea27e
-	0x7ff7c30ea58c
-	0x7ff7c313ed77
-	0x7ff7c313baba
-	0x7ff7c30db0ed
-	0x7ff7c30dbf63
-	0x7ff7c35d5d60
-	0x7ff7c35cfe8a
-	0x7ff7c35f1005
-	0x7ff7c331d71e
-	0x7ff7c3324e1f
-	0x7ff7c330b7c4
-	0x7ff7c330b97f
-	0x7ff7c32f18e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£35.94</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1548,30 +1364,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c35aa235
-	0x7ff7c3302630
-	0x7ff7c30916dd
-	0x7ff7c30ea27e
-	0x7ff7c30ea58c
-	0x7ff7c313ed77
-	0x7ff7c313baba
-	0x7ff7c30db0ed
-	0x7ff7c30dbf63
-	0x7ff7c35d5d60
-	0x7ff7c35cfe8a
-	0x7ff7c35f1005
-	0x7ff7c331d71e
-	0x7ff7c3324e1f
-	0x7ff7c330b7c4
-	0x7ff7c330b97f
-	0x7ff7c32f18e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£39.16</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1581,7 +1374,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>£53.13</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1668,30 +1461,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c35aa235
-	0x7ff7c3302630
-	0x7ff7c30916dd
-	0x7ff7c30ea27e
-	0x7ff7c30ea58c
-	0x7ff7c313ed77
-	0x7ff7c313baba
-	0x7ff7c30db0ed
-	0x7ff7c30dbf63
-	0x7ff7c35d5d60
-	0x7ff7c35cfe8a
-	0x7ff7c35f1005
-	0x7ff7c331d71e
-	0x7ff7c3324e1f
-	0x7ff7c330b7c4
-	0x7ff7c330b97f
-	0x7ff7c32f18e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£41.36</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1788,30 +1558,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c35aa235
-	0x7ff7c3302630
-	0x7ff7c30916dd
-	0x7ff7c30ea27e
-	0x7ff7c30ea58c
-	0x7ff7c313ed77
-	0x7ff7c313baba
-	0x7ff7c30db0ed
-	0x7ff7c30dbf63
-	0x7ff7c35d5d60
-	0x7ff7c35cfe8a
-	0x7ff7c35f1005
-	0x7ff7c331d71e
-	0x7ff7c3324e1f
-	0x7ff7c330b7c4
-	0x7ff7c330b97f
-	0x7ff7c32f18e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£50.37</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1908,30 +1655,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c35aa235
-	0x7ff7c3302630
-	0x7ff7c30916dd
-	0x7ff7c30ea27e
-	0x7ff7c30ea58c
-	0x7ff7c313ed77
-	0x7ff7c313baba
-	0x7ff7c30db0ed
-	0x7ff7c30dbf63
-	0x7ff7c35d5d60
-	0x7ff7c35cfe8a
-	0x7ff7c35f1005
-	0x7ff7c331d71e
-	0x7ff7c3324e1f
-	0x7ff7c330b7c4
-	0x7ff7c330b97f
-	0x7ff7c32f18e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£50.30</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2028,30 +1752,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c35aa235
-	0x7ff7c3302630
-	0x7ff7c30916dd
-	0x7ff7c30ea27e
-	0x7ff7c30ea58c
-	0x7ff7c313ed77
-	0x7ff7c313baba
-	0x7ff7c30db0ed
-	0x7ff7c30dbf63
-	0x7ff7c35d5d60
-	0x7ff7c35cfe8a
-	0x7ff7c35f1005
-	0x7ff7c331d71e
-	0x7ff7c3324e1f
-	0x7ff7c330b7c4
-	0x7ff7c330b97f
-	0x7ff7c32f18e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£58.68</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2148,30 +1849,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c35aa235
-	0x7ff7c3302630
-	0x7ff7c30916dd
-	0x7ff7c30ea27e
-	0x7ff7c30ea58c
-	0x7ff7c313ed77
-	0x7ff7c313baba
-	0x7ff7c30db0ed
-	0x7ff7c30dbf63
-	0x7ff7c35d5d60
-	0x7ff7c35cfe8a
-	0x7ff7c35f1005
-	0x7ff7c331d71e
-	0x7ff7c3324e1f
-	0x7ff7c330b7c4
-	0x7ff7c330b97f
-	0x7ff7c32f18e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£62.87</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2268,30 +1946,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c35aa235
-	0x7ff7c3302630
-	0x7ff7c30916dd
-	0x7ff7c30ea27e
-	0x7ff7c30ea58c
-	0x7ff7c313ed77
-	0x7ff7c313baba
-	0x7ff7c30db0ed
-	0x7ff7c30dbf63
-	0x7ff7c35d5d60
-	0x7ff7c35cfe8a
-	0x7ff7c35f1005
-	0x7ff7c331d71e
-	0x7ff7c3324e1f
-	0x7ff7c330b7c4
-	0x7ff7c330b97f
-	0x7ff7c32f18e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£59.49</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2485,30 +2140,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c35aa235
-	0x7ff7c3302630
-	0x7ff7c30916dd
-	0x7ff7c30ea27e
-	0x7ff7c30ea58c
-	0x7ff7c313ed77
-	0x7ff7c313baba
-	0x7ff7c30db0ed
-	0x7ff7c30dbf63
-	0x7ff7c35d5d60
-	0x7ff7c35cfe8a
-	0x7ff7c35f1005
-	0x7ff7c331d71e
-	0x7ff7c3324e1f
-	0x7ff7c330b7c4
-	0x7ff7c330b97f
-	0x7ff7c32f18e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£1,141.98</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2605,30 +2237,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c35aa235
-	0x7ff7c3302630
-	0x7ff7c30916dd
-	0x7ff7c30ea27e
-	0x7ff7c30ea58c
-	0x7ff7c313ed77
-	0x7ff7c313baba
-	0x7ff7c30db0ed
-	0x7ff7c30dbf63
-	0x7ff7c35d5d60
-	0x7ff7c35cfe8a
-	0x7ff7c35f1005
-	0x7ff7c331d71e
-	0x7ff7c3324e1f
-	0x7ff7c330b7c4
-	0x7ff7c330b97f
-	0x7ff7c32f18e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£34.56</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2725,30 +2334,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c35aa235
-	0x7ff7c3302630
-	0x7ff7c30916dd
-	0x7ff7c30ea27e
-	0x7ff7c30ea58c
-	0x7ff7c313ed77
-	0x7ff7c313baba
-	0x7ff7c30db0ed
-	0x7ff7c30dbf63
-	0x7ff7c35d5d60
-	0x7ff7c35cfe8a
-	0x7ff7c35f1005
-	0x7ff7c331d71e
-	0x7ff7c3324e1f
-	0x7ff7c330b7c4
-	0x7ff7c330b97f
-	0x7ff7c32f18e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£41.09</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2845,30 +2431,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c35aa235
-	0x7ff7c3302630
-	0x7ff7c30916dd
-	0x7ff7c30ea27e
-	0x7ff7c30ea58c
-	0x7ff7c313ed77
-	0x7ff7c313baba
-	0x7ff7c30db0ed
-	0x7ff7c30dbf63
-	0x7ff7c35d5d60
-	0x7ff7c35cfe8a
-	0x7ff7c35f1005
-	0x7ff7c331d71e
-	0x7ff7c3324e1f
-	0x7ff7c330b7c4
-	0x7ff7c330b97f
-	0x7ff7c32f18e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£48.75</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2965,30 +2528,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c35aa235
-	0x7ff7c3302630
-	0x7ff7c30916dd
-	0x7ff7c30ea27e
-	0x7ff7c30ea58c
-	0x7ff7c313ed77
-	0x7ff7c313baba
-	0x7ff7c30db0ed
-	0x7ff7c30dbf63
-	0x7ff7c35d5d60
-	0x7ff7c35cfe8a
-	0x7ff7c35f1005
-	0x7ff7c331d71e
-	0x7ff7c3324e1f
-	0x7ff7c330b7c4
-	0x7ff7c330b97f
-	0x7ff7c32f18e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£53.63</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3085,30 +2625,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c35aa235
-	0x7ff7c3302630
-	0x7ff7c30916dd
-	0x7ff7c30ea27e
-	0x7ff7c30ea58c
-	0x7ff7c313ed77
-	0x7ff7c313baba
-	0x7ff7c30db0ed
-	0x7ff7c30dbf63
-	0x7ff7c35d5d60
-	0x7ff7c35cfe8a
-	0x7ff7c35f1005
-	0x7ff7c331d71e
-	0x7ff7c3324e1f
-	0x7ff7c330b7c4
-	0x7ff7c330b97f
-	0x7ff7c32f18e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£65.53</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3160,14 +2677,14 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>£43.50</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>£43.50</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>£42.50</t>
@@ -3205,30 +2722,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c35aa235
-	0x7ff7c3302630
-	0x7ff7c30916dd
-	0x7ff7c30ea27e
-	0x7ff7c30ea58c
-	0x7ff7c313ed77
-	0x7ff7c313baba
-	0x7ff7c30db0ed
-	0x7ff7c30dbf63
-	0x7ff7c35d5d60
-	0x7ff7c35cfe8a
-	0x7ff7c35f1005
-	0x7ff7c331d71e
-	0x7ff7c3324e1f
-	0x7ff7c330b7c4
-	0x7ff7c330b97f
-	0x7ff7c32f18e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£66.65</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3325,30 +2819,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c35aa235
-	0x7ff7c3302630
-	0x7ff7c30916dd
-	0x7ff7c30ea27e
-	0x7ff7c30ea58c
-	0x7ff7c313ed77
-	0x7ff7c313baba
-	0x7ff7c30db0ed
-	0x7ff7c30dbf63
-	0x7ff7c35d5d60
-	0x7ff7c35cfe8a
-	0x7ff7c35f1005
-	0x7ff7c331d71e
-	0x7ff7c3324e1f
-	0x7ff7c330b7c4
-	0x7ff7c330b97f
-	0x7ff7c32f18e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£1191.68</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3445,30 +2916,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c35aa235
-	0x7ff7c3302630
-	0x7ff7c30916dd
-	0x7ff7c30ea27e
-	0x7ff7c30ea58c
-	0x7ff7c313ed77
-	0x7ff7c313baba
-	0x7ff7c30db0ed
-	0x7ff7c30dbf63
-	0x7ff7c35d5d60
-	0x7ff7c35cfe8a
-	0x7ff7c35f1005
-	0x7ff7c331d71e
-	0x7ff7c3324e1f
-	0x7ff7c330b7c4
-	0x7ff7c330b97f
-	0x7ff7c32f18e8
-	0x7fff71bce8d7
-	0x7fff72a2c53c
-</t>
+          <t>£66.18</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
